--- a/Data/National Accounts/PSA-16IAC_2018PSNA_Qrt.xlsx
+++ b/Data/National Accounts/PSA-16IAC_2018PSNA_Qrt.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28324"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\Shared drives\QNAP\NAP Dissemination\As of January 2026\Tables\Prelim Q4 2025\NAP Q1 2000 to Q4 2025\Qtr\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="I:\Shared drives\QNAP\NAP Dissemination\As of April 2026\Tables\NAP Q1 2000 to Q4 2025\Qtr\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{292F7AB4-E5FE-460D-BB6A-DA7CF136848C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{27D68863-E8DE-4498-91E5-C2F5ED6960DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="794" xr2:uid="{736930C2-BFBB-46C3-AE9E-AECFC8C3145D}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="794" xr2:uid="{736930C2-BFBB-46C3-AE9E-AECFC8C3145D}"/>
   </bookViews>
   <sheets>
     <sheet name="IAC" sheetId="16" r:id="rId1"/>
@@ -683,10 +683,10 @@
     <t>Table 17.7 Gross Value Added in Information and Communication, by Industry</t>
   </si>
   <si>
-    <t>As of January 2026</t>
+    <t>Q1 2000 to Q4 2025</t>
   </si>
   <si>
-    <t>Q1 2000 to Q4 2025</t>
+    <t>As of April 2026</t>
   </si>
 </sst>
 </file>
@@ -735,10 +735,12 @@
       <sz val="12"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="12"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="12"/>
@@ -1229,7 +1231,7 @@
     </row>
     <row r="3" spans="1:179" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A3" s="2" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="4" spans="1:179" s="3" customFormat="1" x14ac:dyDescent="0.2"/>
@@ -1240,7 +1242,7 @@
     </row>
     <row r="6" spans="1:179" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A6" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="7" spans="1:179" s="3" customFormat="1" x14ac:dyDescent="0.2">
@@ -2230,28 +2232,28 @@
         <v>16745.325844222578</v>
       </c>
       <c r="CT12" s="20">
-        <v>13493.331594321164</v>
+        <v>13606.512684674883</v>
       </c>
       <c r="CU12" s="20">
-        <v>18561.046955314821</v>
+        <v>18898.087686574097</v>
       </c>
       <c r="CV12" s="20">
-        <v>12717.749786684817</v>
+        <v>12834.768612134387</v>
       </c>
       <c r="CW12" s="20">
-        <v>18233.999417501887</v>
+        <v>18817.623125185302</v>
       </c>
       <c r="CX12" s="20">
-        <v>14815.541490678501</v>
+        <v>14874.738103335203</v>
       </c>
       <c r="CY12" s="20">
-        <v>21283.905374667534</v>
+        <v>21272.234026064849</v>
       </c>
       <c r="CZ12" s="20">
-        <v>13758.976962772136</v>
+        <v>13876.781179365156</v>
       </c>
       <c r="DA12" s="20">
-        <v>18815.428756081259</v>
+        <v>20564.848885990174</v>
       </c>
       <c r="DB12" s="16"/>
       <c r="DC12" s="16"/>
@@ -2621,28 +2623,28 @@
         <v>191075.01517086301</v>
       </c>
       <c r="CT13" s="22">
-        <v>159797.32442856659</v>
+        <v>159778.62133026213</v>
       </c>
       <c r="CU13" s="22">
-        <v>195716.65821643893</v>
+        <v>195719.67913697558</v>
       </c>
       <c r="CV13" s="22">
-        <v>154611.43058883899</v>
+        <v>154757.49396738189</v>
       </c>
       <c r="CW13" s="22">
-        <v>195691.20295075249</v>
+        <v>195906.42683631941</v>
       </c>
       <c r="CX13" s="22">
-        <v>167288.78395779632</v>
+        <v>167912.22731844703</v>
       </c>
       <c r="CY13" s="22">
-        <v>203186.50101804957</v>
+        <v>202602.48631126032</v>
       </c>
       <c r="CZ13" s="22">
-        <v>160086.10733877539</v>
+        <v>160539.29717549638</v>
       </c>
       <c r="DA13" s="22">
-        <v>201121.1740992268</v>
+        <v>203725.1817495818</v>
       </c>
       <c r="DB13" s="16"/>
       <c r="DC13" s="16"/>
@@ -3192,28 +3194,28 @@
         <v>207820.34101508558</v>
       </c>
       <c r="CT15" s="24">
-        <v>173290.65602288774</v>
+        <v>173385.13401493701</v>
       </c>
       <c r="CU15" s="24">
-        <v>214277.70517175374</v>
+        <v>214617.76682354967</v>
       </c>
       <c r="CV15" s="24">
-        <v>167329.18037552381</v>
+        <v>167592.26257951627</v>
       </c>
       <c r="CW15" s="24">
-        <v>213925.20236825437</v>
+        <v>214724.0499615047</v>
       </c>
       <c r="CX15" s="24">
-        <v>182104.32544847482</v>
+        <v>182786.96542178222</v>
       </c>
       <c r="CY15" s="24">
-        <v>224470.40639271709</v>
+        <v>223874.72033732518</v>
       </c>
       <c r="CZ15" s="24">
-        <v>173845.08430154753</v>
+        <v>174416.07835486153</v>
       </c>
       <c r="DA15" s="24">
-        <v>219936.60285530807</v>
+        <v>224290.03063557198</v>
       </c>
       <c r="DB15" s="16"/>
       <c r="DC15" s="16"/>
@@ -3774,7 +3776,7 @@
     </row>
     <row r="22" spans="1:179" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A22" s="3" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="23" spans="1:179" s="3" customFormat="1" x14ac:dyDescent="0.2"/>
@@ -3785,7 +3787,7 @@
     </row>
     <row r="25" spans="1:179" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A25" s="3" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="26" spans="1:179" s="3" customFormat="1" x14ac:dyDescent="0.2">
@@ -4775,28 +4777,28 @@
         <v>14320.021699058496</v>
       </c>
       <c r="CT31" s="20">
-        <v>11944.723260987335</v>
+        <v>12044.914736547085</v>
       </c>
       <c r="CU31" s="20">
-        <v>17871.593132077411</v>
+        <v>18196.114417568733</v>
       </c>
       <c r="CV31" s="20">
-        <v>10876.154797795662</v>
+        <v>10976.228700899048</v>
       </c>
       <c r="CW31" s="20">
-        <v>15523.972260193084</v>
+        <v>16020.854926525299</v>
       </c>
       <c r="CX31" s="20">
-        <v>13030.949836486267</v>
+        <v>13084.324483296743</v>
       </c>
       <c r="CY31" s="20">
-        <v>20372.731536145649</v>
+        <v>20353.111616449558</v>
       </c>
       <c r="CZ31" s="20">
-        <v>11659.767483152194</v>
+        <v>11760.569547870451</v>
       </c>
       <c r="DA31" s="20">
-        <v>15848.454785164649</v>
+        <v>17325.492828578645</v>
       </c>
       <c r="DB31" s="16"/>
       <c r="DC31" s="16"/>
@@ -5166,28 +5168,28 @@
         <v>188316.72722943159</v>
       </c>
       <c r="CT32" s="22">
-        <v>159711.81286220526</v>
+        <v>159693.11977239902</v>
       </c>
       <c r="CU32" s="22">
-        <v>196585.95410473298</v>
+        <v>196588.98844300234</v>
       </c>
       <c r="CV32" s="22">
-        <v>146066.82946937997</v>
+        <v>146204.82065492231</v>
       </c>
       <c r="CW32" s="22">
-        <v>192492.50558178162</v>
+        <v>192704.21149583976</v>
       </c>
       <c r="CX32" s="22">
-        <v>166714.15927687171</v>
+        <v>167279.61008994636</v>
       </c>
       <c r="CY32" s="22">
-        <v>203366.41988047477</v>
+        <v>202779.56166183675</v>
       </c>
       <c r="CZ32" s="22">
-        <v>150413.03681641744</v>
+        <v>150836.4415358846</v>
       </c>
       <c r="DA32" s="22">
-        <v>196497.0060659234</v>
+        <v>199041.14250187651</v>
       </c>
       <c r="DB32" s="16"/>
       <c r="DC32" s="16"/>
@@ -5737,28 +5739,28 @@
         <v>202636.74892849009</v>
       </c>
       <c r="CT34" s="24">
-        <v>171656.53612319261</v>
+        <v>171738.03450894612</v>
       </c>
       <c r="CU34" s="24">
-        <v>214457.54723681038</v>
+        <v>214785.10286057106</v>
       </c>
       <c r="CV34" s="24">
-        <v>156942.98426717563</v>
+        <v>157181.04935582136</v>
       </c>
       <c r="CW34" s="24">
-        <v>208016.4778419747</v>
+        <v>208725.06642236505</v>
       </c>
       <c r="CX34" s="24">
-        <v>179745.10911335796</v>
+        <v>180363.93457324311</v>
       </c>
       <c r="CY34" s="24">
-        <v>223739.15141662041</v>
+        <v>223132.6732782863</v>
       </c>
       <c r="CZ34" s="24">
-        <v>162072.80429956963</v>
+        <v>162597.01108375506</v>
       </c>
       <c r="DA34" s="24">
-        <v>212345.46085108805</v>
+        <v>216366.63533045514</v>
       </c>
       <c r="DB34" s="16"/>
       <c r="DC34" s="16"/>
@@ -6327,7 +6329,7 @@
     </row>
     <row r="41" spans="1:179" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A41" s="3" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="CX41" s="4"/>
       <c r="CY41" s="4"/>
@@ -6351,7 +6353,7 @@
     </row>
     <row r="44" spans="1:179" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A44" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="CX44" s="4"/>
       <c r="CY44" s="4"/>
@@ -7127,28 +7129,28 @@
         <v>10.236320531789218</v>
       </c>
       <c r="CP50" s="13">
-        <v>0.93025779717952162</v>
+        <v>1.7768535061276793</v>
       </c>
       <c r="CQ50" s="13">
-        <v>7.2573597460801977</v>
+        <v>9.2049922825846409</v>
       </c>
       <c r="CR50" s="13">
-        <v>1.4587623186803569</v>
+        <v>2.3923068054990466</v>
       </c>
       <c r="CS50" s="13">
-        <v>8.8900842368076667</v>
+        <v>12.375377464976012</v>
       </c>
       <c r="CT50" s="13">
-        <v>9.7989876489347267</v>
+        <v>9.3207234509745689</v>
       </c>
       <c r="CU50" s="13">
-        <v>14.669745871059519</v>
+        <v>12.562891964870261</v>
       </c>
       <c r="CV50" s="13">
-        <v>8.1871965839228835</v>
+        <v>8.1186704546088748</v>
       </c>
       <c r="CW50" s="13">
-        <v>3.188709867026148</v>
+        <v>9.2850502381802045</v>
       </c>
       <c r="CX50" s="19"/>
       <c r="CY50" s="19"/>
@@ -7506,28 +7508,28 @@
         <v>5.4139014389514415</v>
       </c>
       <c r="CP51" s="13">
-        <v>5.1050996379211995</v>
+        <v>5.0927978611683216</v>
       </c>
       <c r="CQ51" s="13">
-        <v>7.7297085149927085</v>
+        <v>7.7313713417128724</v>
       </c>
       <c r="CR51" s="13">
-        <v>4.6638583798038553</v>
+        <v>4.7627356536772396</v>
       </c>
       <c r="CS51" s="13">
-        <v>2.4159033957221254</v>
+        <v>2.5285418196282876</v>
       </c>
       <c r="CT51" s="13">
-        <v>4.6881007276054874</v>
+        <v>5.0905471085350911</v>
       </c>
       <c r="CU51" s="13">
-        <v>3.8166617342045157</v>
+        <v>3.5166658787887002</v>
       </c>
       <c r="CV51" s="13">
-        <v>3.5409262621049606</v>
+        <v>3.7360408597293002</v>
       </c>
       <c r="CW51" s="13">
-        <v>2.7747650720103252</v>
+        <v>3.9910660612451352</v>
       </c>
       <c r="CX51" s="19"/>
       <c r="CY51" s="19"/>
@@ -8062,28 +8064,28 @@
         <v>5.786788422367195</v>
       </c>
       <c r="CP53" s="13">
-        <v>4.7676647710112263</v>
+        <v>4.8247840573387464</v>
       </c>
       <c r="CQ53" s="13">
-        <v>7.6886284601985579</v>
+        <v>7.8595317879360778</v>
       </c>
       <c r="CR53" s="13">
-        <v>4.4131635731305323</v>
+        <v>4.5773264832517526</v>
       </c>
       <c r="CS53" s="13">
-        <v>2.9375668057082294</v>
+        <v>3.3219601665064999</v>
       </c>
       <c r="CT53" s="13">
-        <v>5.0860615499216664</v>
+        <v>5.4225129854761605</v>
       </c>
       <c r="CU53" s="13">
-        <v>4.756771691573519</v>
+        <v>4.3132279544154386</v>
       </c>
       <c r="CV53" s="13">
-        <v>3.8940631343562302</v>
+        <v>4.0716770991188156</v>
       </c>
       <c r="CW53" s="13">
-        <v>2.8100478206890074</v>
+        <v>4.4550112927649508</v>
       </c>
       <c r="CX53" s="19"/>
       <c r="CY53" s="19"/>
@@ -8648,7 +8650,7 @@
     </row>
     <row r="60" spans="1:175" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A60" s="3" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="CX60" s="4"/>
       <c r="CY60" s="4"/>
@@ -8672,7 +8674,7 @@
     </row>
     <row r="63" spans="1:175" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A63" s="3" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="CX63" s="4"/>
       <c r="CY63" s="4"/>
@@ -9448,28 +9450,28 @@
         <v>4.8711915409062243</v>
       </c>
       <c r="CP69" s="13">
-        <v>-1.2476789279324976</v>
+        <v>-0.41935159485178986</v>
       </c>
       <c r="CQ69" s="13">
-        <v>5.0774681290466077</v>
+        <v>6.9855171083066807</v>
       </c>
       <c r="CR69" s="13">
-        <v>0.65648567807028257</v>
+        <v>1.5826482402762139</v>
       </c>
       <c r="CS69" s="13">
-        <v>8.4074632457697049</v>
+        <v>11.877309009794516</v>
       </c>
       <c r="CT69" s="13">
-        <v>9.0937776603553004</v>
+        <v>8.6294487714042987</v>
       </c>
       <c r="CU69" s="13">
-        <v>13.995050052806917</v>
+        <v>11.854163748268135</v>
       </c>
       <c r="CV69" s="13">
-        <v>7.2048688155427243</v>
+        <v>7.1458136336678137</v>
       </c>
       <c r="CW69" s="13">
-        <v>2.0902029424750452</v>
+        <v>8.1433725480735148</v>
       </c>
       <c r="CX69" s="19"/>
       <c r="CY69" s="19"/>
@@ -9827,28 +9829,28 @@
         <v>4.7657253459610871</v>
       </c>
       <c r="CP70" s="13">
-        <v>4.663338792369089</v>
+        <v>4.6510887204651539</v>
       </c>
       <c r="CQ70" s="13">
-        <v>7.207762252807683</v>
+        <v>7.2094170231968349</v>
       </c>
       <c r="CR70" s="13">
-        <v>4.1905721984998365</v>
+        <v>4.2890023529177341</v>
       </c>
       <c r="CS70" s="13">
-        <v>2.2174229627846813</v>
+        <v>2.329843095171654</v>
       </c>
       <c r="CT70" s="13">
-        <v>4.3843634914518645</v>
+        <v>4.7506682369033371</v>
       </c>
       <c r="CU70" s="13">
-        <v>3.4491099868352961</v>
+        <v>3.1489928646889922</v>
       </c>
       <c r="CV70" s="13">
-        <v>2.9754923570437057</v>
+        <v>3.1678988833712936</v>
       </c>
       <c r="CW70" s="13">
-        <v>2.0803409836859714</v>
+        <v>3.2884237229934996</v>
       </c>
       <c r="CX70" s="19"/>
       <c r="CY70" s="19"/>
@@ -10382,28 +10384,28 @@
         <v>4.7731715105651062</v>
       </c>
       <c r="CP72" s="13">
-        <v>4.2292084541467148</v>
+        <v>4.2786939699868185</v>
       </c>
       <c r="CQ72" s="13">
-        <v>7.0269428527606266</v>
+        <v>7.1904123947610401</v>
       </c>
       <c r="CR72" s="13">
-        <v>3.9376762388956195</v>
+        <v>4.0953381581141315</v>
       </c>
       <c r="CS72" s="13">
-        <v>2.6548634154129189</v>
+        <v>3.0045475591515327</v>
       </c>
       <c r="CT72" s="13">
-        <v>4.7120681640461726</v>
+        <v>5.0227080384151321</v>
       </c>
       <c r="CU72" s="13">
-        <v>4.3279447608159956</v>
+        <v>3.8864755080961544</v>
       </c>
       <c r="CV72" s="13">
-        <v>3.2685883069874251</v>
+        <v>3.445683655968736</v>
       </c>
       <c r="CW72" s="13">
-        <v>2.0810769675669434</v>
+        <v>3.6610690987286745</v>
       </c>
       <c r="CX72" s="19"/>
       <c r="CY72" s="19"/>
@@ -10959,7 +10961,7 @@
     </row>
     <row r="78" spans="1:175" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A78" s="3" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="CX78" s="4"/>
       <c r="CY78" s="4"/>
@@ -10979,7 +10981,7 @@
     </row>
     <row r="81" spans="1:179" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A81" s="3" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="82" spans="1:179" s="3" customFormat="1" x14ac:dyDescent="0.2">
@@ -11760,28 +11762,28 @@
         <v>116.93645579687593</v>
       </c>
       <c r="CT87" s="13">
-        <v>112.96479038900583</v>
+        <v>112.96479038900577</v>
       </c>
       <c r="CU87" s="13">
-        <v>103.85781960311039</v>
+        <v>103.8578196031104</v>
       </c>
       <c r="CV87" s="13">
-        <v>116.93240877062917</v>
+        <v>116.9324087706291</v>
       </c>
       <c r="CW87" s="13">
         <v>117.45704715189369</v>
       </c>
       <c r="CX87" s="13">
-        <v>113.69502359064749</v>
+        <v>113.68365346123963</v>
       </c>
       <c r="CY87" s="13">
-        <v>104.47251678993199</v>
+        <v>104.5158815366219</v>
       </c>
       <c r="CZ87" s="13">
-        <v>118.0038708546564</v>
+        <v>117.9941253940197</v>
       </c>
       <c r="DA87" s="13">
-        <v>118.72090377980523</v>
+        <v>118.69705000291918</v>
       </c>
       <c r="DB87" s="16"/>
       <c r="DC87" s="16"/>
@@ -12157,22 +12159,22 @@
         <v>99.557803662905158</v>
       </c>
       <c r="CV88" s="13">
-        <v>105.84978886068738</v>
+        <v>105.84978886068737</v>
       </c>
       <c r="CW88" s="13">
         <v>101.66172566526851</v>
       </c>
       <c r="CX88" s="13">
-        <v>100.34467659100885</v>
+        <v>100.37817952119836</v>
       </c>
       <c r="CY88" s="13">
-        <v>99.911529709511072</v>
+        <v>99.912675937789174</v>
       </c>
       <c r="CZ88" s="13">
-        <v>106.43100540158905</v>
+        <v>106.4326999104546</v>
       </c>
       <c r="DA88" s="13">
-        <v>102.35330203033833</v>
+        <v>102.35330203033834</v>
       </c>
       <c r="DB88" s="16"/>
       <c r="DC88" s="16"/>
@@ -12722,28 +12724,28 @@
         <v>102.55807108730548</v>
       </c>
       <c r="CT90" s="13">
-        <v>100.95197068320334</v>
+        <v>100.95907671862001</v>
       </c>
       <c r="CU90" s="13">
-        <v>99.916140948465639</v>
+        <v>99.92209141379324</v>
       </c>
       <c r="CV90" s="13">
-        <v>106.61781484329811</v>
+        <v>106.62370767109866</v>
       </c>
       <c r="CW90" s="13">
-        <v>102.84050791916994</v>
+        <v>102.87410785966667</v>
       </c>
       <c r="CX90" s="13">
-        <v>101.31253436978305</v>
+        <v>101.3434120597736</v>
       </c>
       <c r="CY90" s="13">
-        <v>100.32683371303889</v>
+        <v>100.33255867378661</v>
       </c>
       <c r="CZ90" s="13">
-        <v>107.26357518946759</v>
+        <v>107.26893267737768</v>
       </c>
       <c r="DA90" s="13">
-        <v>103.57490194223811</v>
+        <v>103.66202270189</v>
       </c>
       <c r="DB90" s="16"/>
       <c r="DC90" s="16"/>
@@ -12944,7 +12946,7 @@
     </row>
     <row r="97" spans="1:179" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A97" s="3" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="98" spans="1:179" s="3" customFormat="1" x14ac:dyDescent="0.2"/>
@@ -12955,7 +12957,7 @@
     </row>
     <row r="100" spans="1:179" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A100" s="3" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="101" spans="1:179" s="3" customFormat="1" x14ac:dyDescent="0.2">
@@ -13736,28 +13738,28 @@
         <v>8.057597135309793</v>
       </c>
       <c r="CT106" s="13">
-        <v>7.7865315441699305</v>
+        <v>7.8475659184845057</v>
       </c>
       <c r="CU106" s="13">
-        <v>8.6621456676686268</v>
+        <v>8.8054628310951379</v>
       </c>
       <c r="CV106" s="13">
-        <v>7.6004375077576816</v>
+        <v>7.6583300533010989</v>
       </c>
       <c r="CW106" s="13">
-        <v>8.5235396370520107</v>
+        <v>8.7636308688099387</v>
       </c>
       <c r="CX106" s="13">
-        <v>8.1357438678031073</v>
+        <v>8.137745527429507</v>
       </c>
       <c r="CY106" s="13">
-        <v>9.481831354388321</v>
+        <v>9.5018472804846947</v>
       </c>
       <c r="CZ106" s="13">
-        <v>7.9145044670381042</v>
+        <v>7.9561364469690048</v>
       </c>
       <c r="DA106" s="13">
-        <v>8.5549328814811041</v>
+        <v>9.1688644509590738</v>
       </c>
       <c r="DB106" s="16"/>
       <c r="DC106" s="16"/>
@@ -14127,28 +14129,28 @@
         <v>91.942402864690209</v>
       </c>
       <c r="CT107" s="13">
-        <v>92.213468455830068</v>
+        <v>92.152434081515494</v>
       </c>
       <c r="CU107" s="13">
-        <v>91.337854332331375</v>
+        <v>91.194537168904873</v>
       </c>
       <c r="CV107" s="13">
-        <v>92.39956249224231</v>
+        <v>92.3416699466989</v>
       </c>
       <c r="CW107" s="13">
-        <v>91.476460362948004</v>
+        <v>91.23636913119006</v>
       </c>
       <c r="CX107" s="13">
-        <v>91.8642561321969</v>
+        <v>91.862254472570498</v>
       </c>
       <c r="CY107" s="13">
-        <v>90.518168645611681</v>
+        <v>90.498152719515303</v>
       </c>
       <c r="CZ107" s="13">
-        <v>92.085495532961886</v>
+        <v>92.043863553031002</v>
       </c>
       <c r="DA107" s="13">
-        <v>91.445067118518892</v>
+        <v>90.831135549040923</v>
       </c>
       <c r="DB107" s="16"/>
       <c r="DC107" s="16"/>
@@ -15280,7 +15282,7 @@
     </row>
     <row r="116" spans="1:179" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A116" s="3" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="117" spans="1:179" s="3" customFormat="1" x14ac:dyDescent="0.2"/>
@@ -15291,7 +15293,7 @@
     </row>
     <row r="119" spans="1:179" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A119" s="3" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="120" spans="1:179" s="3" customFormat="1" x14ac:dyDescent="0.2">
@@ -16072,28 +16074,28 @@
         <v>7.0668433908362731</v>
       </c>
       <c r="CT125" s="13">
-        <v>6.9585018611904044</v>
+        <v>7.0135394125054136</v>
       </c>
       <c r="CU125" s="13">
-        <v>8.3333943534955512</v>
+        <v>8.4717767551043064</v>
       </c>
       <c r="CV125" s="13">
-        <v>6.9300038154495525</v>
+        <v>6.9831756091991837</v>
       </c>
       <c r="CW125" s="13">
-        <v>7.4628569915438554</v>
+        <v>7.6755778312252829</v>
       </c>
       <c r="CX125" s="13">
-        <v>7.2496825648080216</v>
+        <v>7.2544017817394595</v>
       </c>
       <c r="CY125" s="13">
-        <v>9.1055728991346587</v>
+        <v>9.1215290514919758</v>
       </c>
       <c r="CZ125" s="13">
-        <v>7.1941542157811327</v>
+        <v>7.2329555564908166</v>
       </c>
       <c r="DA125" s="13">
-        <v>7.4635241655948219</v>
+        <v>8.0074697293866723</v>
       </c>
       <c r="DB125" s="16"/>
       <c r="DC125" s="16"/>
@@ -16463,28 +16465,28 @@
         <v>92.933156609163731</v>
       </c>
       <c r="CT126" s="13">
-        <v>93.041498138809587</v>
+        <v>92.986460587494577</v>
       </c>
       <c r="CU126" s="13">
-        <v>91.666605646504451</v>
+        <v>91.528223244895699</v>
       </c>
       <c r="CV126" s="13">
-        <v>93.069996184550448</v>
+        <v>93.016824390800807</v>
       </c>
       <c r="CW126" s="13">
-        <v>92.537143008456141</v>
+        <v>92.324422168774717</v>
       </c>
       <c r="CX126" s="13">
-        <v>92.750317435191988</v>
+        <v>92.74559821826054</v>
       </c>
       <c r="CY126" s="13">
-        <v>90.894427100865343</v>
+        <v>90.878470948508024</v>
       </c>
       <c r="CZ126" s="13">
-        <v>92.805845784218874</v>
+        <v>92.767044443509178</v>
       </c>
       <c r="DA126" s="13">
-        <v>92.536475834405181</v>
+        <v>91.992530270613344</v>
       </c>
       <c r="DB126" s="16"/>
       <c r="DC126" s="16"/>

--- a/Data/National Accounts/PSA-16IAC_2018PSNA_Qrt.xlsx
+++ b/Data/National Accounts/PSA-16IAC_2018PSNA_Qrt.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28324"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="I:\Shared drives\QNAP\NAP Dissemination\As of April 2026\Tables\NAP Q1 2000 to Q4 2025\Qtr\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\Shared drives\QNAP\NAP Dissemination\As of May 2026\Tables\NAP Q1 2000 to Q1 2026\Qtr\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{27D68863-E8DE-4498-91E5-C2F5ED6960DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F207A125-3B0C-41FB-9777-0CC002C2BCB4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="794" xr2:uid="{736930C2-BFBB-46C3-AE9E-AECFC8C3145D}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="794" xr2:uid="{736930C2-BFBB-46C3-AE9E-AECFC8C3145D}"/>
   </bookViews>
   <sheets>
     <sheet name="IAC" sheetId="16" r:id="rId1"/>
@@ -353,7 +353,7 @@
     <definedName name="pet">#REF!</definedName>
     <definedName name="plastic">#REF!</definedName>
     <definedName name="ply">#REF!</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">IAC!$A$1:$DA$131</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">IAC!$A$1:$DB$131</definedName>
     <definedName name="_xlnm.Print_Area">#REF!</definedName>
     <definedName name="PRINT_AREA_MI">#REF!</definedName>
     <definedName name="Print_Titles_MI">#REF!,#REF!</definedName>
@@ -527,7 +527,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="846" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="855" uniqueCount="54">
   <si>
     <t>National Accounts of the Philippines</t>
   </si>
@@ -683,10 +683,13 @@
     <t>Table 17.7 Gross Value Added in Information and Communication, by Industry</t>
   </si>
   <si>
-    <t>Q1 2000 to Q4 2025</t>
+    <t>Q1 2000 to Q1 2026</t>
   </si>
   <si>
-    <t>As of April 2026</t>
+    <t>As of May 2026</t>
+  </si>
+  <si>
+    <t>2025 - 2026</t>
   </si>
 </sst>
 </file>
@@ -1215,8 +1218,8 @@
   <sheetFormatPr defaultColWidth="10" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="61.28515625" style="3" customWidth="1"/>
-    <col min="2" max="105" width="13" style="17" customWidth="1"/>
-    <col min="106" max="16384" width="10" style="17"/>
+    <col min="2" max="106" width="13" style="17" customWidth="1"/>
+    <col min="107" max="16384" width="10" style="17"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:179" s="3" customFormat="1" x14ac:dyDescent="0.2">
@@ -1353,6 +1356,7 @@
       <c r="CY7" s="21"/>
       <c r="CZ7" s="21"/>
       <c r="DA7" s="21"/>
+      <c r="DB7" s="21"/>
     </row>
     <row r="8" spans="1:179" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B8" s="21"/>
@@ -1459,6 +1463,7 @@
       <c r="CY8" s="21"/>
       <c r="CZ8" s="21"/>
       <c r="DA8" s="21"/>
+      <c r="DB8" s="21"/>
     </row>
     <row r="9" spans="1:179" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A9" s="14"/>
@@ -1618,6 +1623,9 @@
       <c r="CY9" s="28"/>
       <c r="CZ9" s="28"/>
       <c r="DA9" s="28"/>
+      <c r="DB9" s="28">
+        <v>2026</v>
+      </c>
     </row>
     <row r="10" spans="1:179" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A10" s="5" t="s">
@@ -1934,6 +1942,9 @@
       </c>
       <c r="DA10" s="12" t="s">
         <v>5</v>
+      </c>
+      <c r="DB10" s="12" t="s">
+        <v>2</v>
       </c>
     </row>
     <row r="11" spans="1:179" s="3" customFormat="1" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
@@ -2255,7 +2266,9 @@
       <c r="DA12" s="20">
         <v>20564.848885990174</v>
       </c>
-      <c r="DB12" s="16"/>
+      <c r="DB12" s="20">
+        <v>16493.870679350446</v>
+      </c>
       <c r="DC12" s="16"/>
       <c r="DD12" s="16"/>
       <c r="DE12" s="16"/>
@@ -2646,7 +2659,9 @@
       <c r="DA13" s="22">
         <v>203725.1817495818</v>
       </c>
-      <c r="DB13" s="16"/>
+      <c r="DB13" s="22">
+        <v>176256.2919337246</v>
+      </c>
       <c r="DC13" s="16"/>
       <c r="DD13" s="16"/>
       <c r="DE13" s="16"/>
@@ -2826,7 +2841,7 @@
       <c r="CY14" s="23"/>
       <c r="CZ14" s="23"/>
       <c r="DA14" s="23"/>
-      <c r="DB14" s="16"/>
+      <c r="DB14" s="23"/>
       <c r="DC14" s="16"/>
       <c r="DD14" s="16"/>
       <c r="DE14" s="16"/>
@@ -3217,7 +3232,9 @@
       <c r="DA15" s="24">
         <v>224290.03063557198</v>
       </c>
-      <c r="DB15" s="16"/>
+      <c r="DB15" s="24">
+        <v>192750.16261307505</v>
+      </c>
       <c r="DC15" s="16"/>
       <c r="DD15" s="16"/>
       <c r="DE15" s="16"/>
@@ -3398,6 +3415,7 @@
       <c r="CY16" s="10"/>
       <c r="CZ16" s="10"/>
       <c r="DA16" s="10"/>
+      <c r="DB16" s="10"/>
     </row>
     <row r="17" spans="1:179" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A17" s="11" t="s">
@@ -3898,6 +3916,7 @@
       <c r="CY26" s="21"/>
       <c r="CZ26" s="21"/>
       <c r="DA26" s="21"/>
+      <c r="DB26" s="21"/>
     </row>
     <row r="27" spans="1:179" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B27" s="21"/>
@@ -4004,6 +4023,7 @@
       <c r="CY27" s="21"/>
       <c r="CZ27" s="21"/>
       <c r="DA27" s="21"/>
+      <c r="DB27" s="21"/>
     </row>
     <row r="28" spans="1:179" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A28" s="14"/>
@@ -4163,6 +4183,9 @@
       <c r="CY28" s="28"/>
       <c r="CZ28" s="28"/>
       <c r="DA28" s="28"/>
+      <c r="DB28" s="28">
+        <v>2026</v>
+      </c>
     </row>
     <row r="29" spans="1:179" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A29" s="5" t="s">
@@ -4479,6 +4502,9 @@
       </c>
       <c r="DA29" s="12" t="s">
         <v>5</v>
+      </c>
+      <c r="DB29" s="12" t="s">
+        <v>2</v>
       </c>
     </row>
     <row r="30" spans="1:179" s="3" customFormat="1" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
@@ -4800,7 +4826,9 @@
       <c r="DA31" s="20">
         <v>17325.492828578645</v>
       </c>
-      <c r="DB31" s="16"/>
+      <c r="DB31" s="20">
+        <v>14156.062799208608</v>
+      </c>
       <c r="DC31" s="16"/>
       <c r="DD31" s="16"/>
       <c r="DE31" s="16"/>
@@ -5191,7 +5219,9 @@
       <c r="DA32" s="22">
         <v>199041.14250187651</v>
       </c>
-      <c r="DB32" s="16"/>
+      <c r="DB32" s="22">
+        <v>174128.03080381802</v>
+      </c>
       <c r="DC32" s="16"/>
       <c r="DD32" s="16"/>
       <c r="DE32" s="16"/>
@@ -5762,7 +5792,9 @@
       <c r="DA34" s="24">
         <v>216366.63533045514</v>
       </c>
-      <c r="DB34" s="16"/>
+      <c r="DB34" s="24">
+        <v>188284.09360302665</v>
+      </c>
       <c r="DC34" s="16"/>
       <c r="DD34" s="16"/>
       <c r="DE34" s="16"/>
@@ -5943,6 +5975,7 @@
       <c r="CY35" s="10"/>
       <c r="CZ35" s="10"/>
       <c r="DA35" s="10"/>
+      <c r="DB35" s="10"/>
     </row>
     <row r="36" spans="1:179" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A36" s="11" t="s">
@@ -6234,7 +6267,7 @@
       <c r="CY38" s="15"/>
       <c r="CZ38" s="15"/>
       <c r="DA38" s="15"/>
-      <c r="DB38" s="16"/>
+      <c r="DB38" s="15"/>
       <c r="DC38" s="16"/>
       <c r="DD38" s="16"/>
       <c r="DE38" s="16"/>
@@ -6317,6 +6350,7 @@
       <c r="CY39" s="4"/>
       <c r="CZ39" s="4"/>
       <c r="DA39" s="4"/>
+      <c r="DB39" s="4"/>
     </row>
     <row r="40" spans="1:179" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A40" s="3" t="s">
@@ -6326,6 +6360,7 @@
       <c r="CY40" s="4"/>
       <c r="CZ40" s="4"/>
       <c r="DA40" s="4"/>
+      <c r="DB40" s="4"/>
     </row>
     <row r="41" spans="1:179" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A41" s="3" t="s">
@@ -6335,12 +6370,14 @@
       <c r="CY41" s="4"/>
       <c r="CZ41" s="4"/>
       <c r="DA41" s="4"/>
+      <c r="DB41" s="4"/>
     </row>
     <row r="42" spans="1:179" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="CX42" s="4"/>
       <c r="CY42" s="4"/>
       <c r="CZ42" s="4"/>
       <c r="DA42" s="4"/>
+      <c r="DB42" s="4"/>
     </row>
     <row r="43" spans="1:179" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A43" s="3" t="s">
@@ -6350,6 +6387,7 @@
       <c r="CY43" s="4"/>
       <c r="CZ43" s="4"/>
       <c r="DA43" s="4"/>
+      <c r="DB43" s="4"/>
     </row>
     <row r="44" spans="1:179" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A44" s="1" t="s">
@@ -6359,6 +6397,7 @@
       <c r="CY44" s="4"/>
       <c r="CZ44" s="4"/>
       <c r="DA44" s="4"/>
+      <c r="DB44" s="4"/>
     </row>
     <row r="45" spans="1:179" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A45" s="3" t="s">
@@ -6368,12 +6407,14 @@
       <c r="CY45" s="4"/>
       <c r="CZ45" s="4"/>
       <c r="DA45" s="4"/>
+      <c r="DB45" s="4"/>
     </row>
     <row r="46" spans="1:179" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="CX46" s="4"/>
       <c r="CY46" s="4"/>
       <c r="CZ46" s="4"/>
       <c r="DA46" s="4"/>
+      <c r="DB46" s="4"/>
     </row>
     <row r="47" spans="1:179" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A47" s="14"/>
@@ -6527,10 +6568,13 @@
       <c r="CU47" s="28"/>
       <c r="CV47" s="28"/>
       <c r="CW47" s="28"/>
-      <c r="CX47" s="29"/>
+      <c r="CX47" s="28" t="s">
+        <v>53</v>
+      </c>
       <c r="CY47" s="29"/>
       <c r="CZ47" s="29"/>
       <c r="DA47" s="29"/>
+      <c r="DB47" s="29"/>
     </row>
     <row r="48" spans="1:179" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A48" s="5" t="s">
@@ -6836,17 +6880,20 @@
       <c r="CW48" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="CX48" s="30"/>
+      <c r="CX48" s="5" t="s">
+        <v>2</v>
+      </c>
       <c r="CY48" s="30"/>
       <c r="CZ48" s="30"/>
       <c r="DA48" s="30"/>
+      <c r="DB48" s="30"/>
     </row>
     <row r="49" spans="1:175" s="3" customFormat="1" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A49" s="6"/>
-      <c r="CX49" s="4"/>
       <c r="CY49" s="4"/>
       <c r="CZ49" s="4"/>
       <c r="DA49" s="4"/>
+      <c r="DB49" s="4"/>
     </row>
     <row r="50" spans="1:175" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A50" s="3" t="s">
@@ -7152,11 +7199,13 @@
       <c r="CW50" s="13">
         <v>9.2850502381802045</v>
       </c>
-      <c r="CX50" s="19"/>
+      <c r="CX50" s="13">
+        <v>10.885116529562296</v>
+      </c>
       <c r="CY50" s="19"/>
       <c r="CZ50" s="19"/>
       <c r="DA50" s="19"/>
-      <c r="DB50" s="16"/>
+      <c r="DB50" s="19"/>
       <c r="DC50" s="16"/>
       <c r="DD50" s="16"/>
       <c r="DE50" s="16"/>
@@ -7531,11 +7580,13 @@
       <c r="CW51" s="13">
         <v>3.9910660612451352</v>
       </c>
-      <c r="CX51" s="19"/>
+      <c r="CX51" s="13">
+        <v>4.9693013716344723</v>
+      </c>
       <c r="CY51" s="19"/>
       <c r="CZ51" s="19"/>
       <c r="DA51" s="19"/>
-      <c r="DB51" s="16"/>
+      <c r="DB51" s="19"/>
       <c r="DC51" s="16"/>
       <c r="DD51" s="16"/>
       <c r="DE51" s="16"/>
@@ -7708,11 +7759,11 @@
       <c r="CU52" s="8"/>
       <c r="CV52" s="8"/>
       <c r="CW52" s="8"/>
-      <c r="CX52" s="7"/>
+      <c r="CX52" s="8"/>
       <c r="CY52" s="7"/>
       <c r="CZ52" s="7"/>
       <c r="DA52" s="7"/>
-      <c r="DB52" s="16"/>
+      <c r="DB52" s="7"/>
       <c r="DC52" s="16"/>
       <c r="DD52" s="16"/>
       <c r="DE52" s="16"/>
@@ -8087,11 +8138,13 @@
       <c r="CW53" s="13">
         <v>4.4550112927649508</v>
       </c>
-      <c r="CX53" s="19"/>
+      <c r="CX53" s="13">
+        <v>5.4507153550597423</v>
+      </c>
       <c r="CY53" s="19"/>
       <c r="CZ53" s="19"/>
       <c r="DA53" s="19"/>
-      <c r="DB53" s="16"/>
+      <c r="DB53" s="19"/>
       <c r="DC53" s="16"/>
       <c r="DD53" s="16"/>
       <c r="DE53" s="16"/>
@@ -8264,19 +8317,20 @@
       <c r="CU54" s="10"/>
       <c r="CV54" s="10"/>
       <c r="CW54" s="10"/>
-      <c r="CX54" s="31"/>
+      <c r="CX54" s="10"/>
       <c r="CY54" s="31"/>
       <c r="CZ54" s="31"/>
       <c r="DA54" s="31"/>
+      <c r="DB54" s="31"/>
     </row>
     <row r="55" spans="1:175" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A55" s="11" t="s">
         <v>6</v>
       </c>
-      <c r="CX55" s="4"/>
       <c r="CY55" s="4"/>
       <c r="CZ55" s="4"/>
       <c r="DA55" s="4"/>
+      <c r="DB55" s="4"/>
     </row>
     <row r="56" spans="1:175" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B56" s="16"/>
@@ -8379,11 +8433,11 @@
       <c r="CU56" s="16"/>
       <c r="CV56" s="16"/>
       <c r="CW56" s="16"/>
-      <c r="CX56" s="15"/>
+      <c r="CX56" s="16"/>
       <c r="CY56" s="15"/>
       <c r="CZ56" s="15"/>
       <c r="DA56" s="15"/>
-      <c r="DB56" s="16"/>
+      <c r="DB56" s="15"/>
       <c r="DC56" s="16"/>
       <c r="DD56" s="16"/>
       <c r="DE56" s="16"/>
@@ -8555,11 +8609,11 @@
       <c r="CU57" s="16"/>
       <c r="CV57" s="16"/>
       <c r="CW57" s="16"/>
-      <c r="CX57" s="15"/>
+      <c r="CX57" s="16"/>
       <c r="CY57" s="15"/>
       <c r="CZ57" s="15"/>
       <c r="DA57" s="15"/>
-      <c r="DB57" s="16"/>
+      <c r="DB57" s="15"/>
       <c r="DC57" s="16"/>
       <c r="DD57" s="16"/>
       <c r="DE57" s="16"/>
@@ -8634,67 +8688,67 @@
       <c r="A58" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="CX58" s="4"/>
       <c r="CY58" s="4"/>
       <c r="CZ58" s="4"/>
       <c r="DA58" s="4"/>
+      <c r="DB58" s="4"/>
     </row>
     <row r="59" spans="1:175" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A59" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="CX59" s="4"/>
       <c r="CY59" s="4"/>
       <c r="CZ59" s="4"/>
       <c r="DA59" s="4"/>
+      <c r="DB59" s="4"/>
     </row>
     <row r="60" spans="1:175" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A60" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="CX60" s="4"/>
       <c r="CY60" s="4"/>
       <c r="CZ60" s="4"/>
       <c r="DA60" s="4"/>
+      <c r="DB60" s="4"/>
     </row>
     <row r="61" spans="1:175" s="3" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="CX61" s="4"/>
       <c r="CY61" s="4"/>
       <c r="CZ61" s="4"/>
       <c r="DA61" s="4"/>
+      <c r="DB61" s="4"/>
     </row>
     <row r="62" spans="1:175" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A62" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="CX62" s="4"/>
       <c r="CY62" s="4"/>
       <c r="CZ62" s="4"/>
       <c r="DA62" s="4"/>
+      <c r="DB62" s="4"/>
     </row>
     <row r="63" spans="1:175" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A63" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="CX63" s="4"/>
       <c r="CY63" s="4"/>
       <c r="CZ63" s="4"/>
       <c r="DA63" s="4"/>
+      <c r="DB63" s="4"/>
     </row>
     <row r="64" spans="1:175" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A64" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="CX64" s="4"/>
       <c r="CY64" s="4"/>
       <c r="CZ64" s="4"/>
       <c r="DA64" s="4"/>
+      <c r="DB64" s="4"/>
     </row>
     <row r="65" spans="1:175" s="3" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="CX65" s="4"/>
       <c r="CY65" s="4"/>
       <c r="CZ65" s="4"/>
       <c r="DA65" s="4"/>
+      <c r="DB65" s="4"/>
     </row>
     <row r="66" spans="1:175" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A66" s="14"/>
@@ -8848,10 +8902,13 @@
       <c r="CU66" s="28"/>
       <c r="CV66" s="28"/>
       <c r="CW66" s="28"/>
-      <c r="CX66" s="29"/>
+      <c r="CX66" s="28" t="s">
+        <v>53</v>
+      </c>
       <c r="CY66" s="29"/>
       <c r="CZ66" s="29"/>
       <c r="DA66" s="29"/>
+      <c r="DB66" s="29"/>
     </row>
     <row r="67" spans="1:175" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A67" s="5" t="s">
@@ -9157,17 +9214,20 @@
       <c r="CW67" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="CX67" s="30"/>
+      <c r="CX67" s="5" t="s">
+        <v>2</v>
+      </c>
       <c r="CY67" s="30"/>
       <c r="CZ67" s="30"/>
       <c r="DA67" s="30"/>
+      <c r="DB67" s="30"/>
     </row>
     <row r="68" spans="1:175" s="3" customFormat="1" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A68" s="6"/>
-      <c r="CX68" s="4"/>
       <c r="CY68" s="4"/>
       <c r="CZ68" s="4"/>
       <c r="DA68" s="4"/>
+      <c r="DB68" s="4"/>
     </row>
     <row r="69" spans="1:175" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A69" s="3" t="s">
@@ -9473,11 +9533,13 @@
       <c r="CW69" s="13">
         <v>8.1433725480735148</v>
       </c>
-      <c r="CX69" s="19"/>
+      <c r="CX69" s="13">
+        <v>8.1910099163317938</v>
+      </c>
       <c r="CY69" s="19"/>
       <c r="CZ69" s="19"/>
       <c r="DA69" s="19"/>
-      <c r="DB69" s="16"/>
+      <c r="DB69" s="19"/>
       <c r="DC69" s="16"/>
       <c r="DD69" s="16"/>
       <c r="DE69" s="16"/>
@@ -9852,11 +9914,13 @@
       <c r="CW70" s="13">
         <v>3.2884237229934996</v>
       </c>
-      <c r="CX70" s="19"/>
+      <c r="CX70" s="13">
+        <v>4.0939961004148984</v>
+      </c>
       <c r="CY70" s="19"/>
       <c r="CZ70" s="19"/>
       <c r="DA70" s="19"/>
-      <c r="DB70" s="16"/>
+      <c r="DB70" s="19"/>
       <c r="DC70" s="16"/>
       <c r="DD70" s="16"/>
       <c r="DE70" s="16"/>
@@ -10028,11 +10092,11 @@
       <c r="CU71" s="8"/>
       <c r="CV71" s="8"/>
       <c r="CW71" s="8"/>
-      <c r="CX71" s="7"/>
+      <c r="CX71" s="8"/>
       <c r="CY71" s="7"/>
       <c r="CZ71" s="7"/>
       <c r="DA71" s="7"/>
-      <c r="DB71" s="16"/>
+      <c r="DB71" s="7"/>
       <c r="DC71" s="16"/>
       <c r="DD71" s="16"/>
       <c r="DE71" s="16"/>
@@ -10407,11 +10471,13 @@
       <c r="CW72" s="13">
         <v>3.6610690987286745</v>
       </c>
-      <c r="CX72" s="19"/>
+      <c r="CX72" s="13">
+        <v>4.3912099436748946</v>
+      </c>
       <c r="CY72" s="19"/>
       <c r="CZ72" s="19"/>
       <c r="DA72" s="19"/>
-      <c r="DB72" s="16"/>
+      <c r="DB72" s="19"/>
       <c r="DC72" s="16"/>
       <c r="DD72" s="16"/>
       <c r="DE72" s="16"/>
@@ -10584,19 +10650,20 @@
       <c r="CU73" s="10"/>
       <c r="CV73" s="10"/>
       <c r="CW73" s="10"/>
-      <c r="CX73" s="31"/>
+      <c r="CX73" s="10"/>
       <c r="CY73" s="31"/>
       <c r="CZ73" s="31"/>
       <c r="DA73" s="31"/>
+      <c r="DB73" s="31"/>
     </row>
     <row r="74" spans="1:175" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A74" s="11" t="s">
         <v>6</v>
       </c>
-      <c r="CX74" s="4"/>
       <c r="CY74" s="4"/>
       <c r="CZ74" s="4"/>
       <c r="DA74" s="4"/>
+      <c r="DB74" s="4"/>
     </row>
     <row r="75" spans="1:175" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B75" s="16"/>
@@ -10703,7 +10770,7 @@
       <c r="CY75" s="15"/>
       <c r="CZ75" s="15"/>
       <c r="DA75" s="15"/>
-      <c r="DB75" s="16"/>
+      <c r="DB75" s="15"/>
       <c r="DC75" s="16"/>
       <c r="DD75" s="16"/>
       <c r="DE75" s="16"/>
@@ -10879,7 +10946,7 @@
       <c r="CY76" s="15"/>
       <c r="CZ76" s="15"/>
       <c r="DA76" s="15"/>
-      <c r="DB76" s="16"/>
+      <c r="DB76" s="15"/>
       <c r="DC76" s="16"/>
       <c r="DD76" s="16"/>
       <c r="DE76" s="16"/>
@@ -10958,6 +11025,7 @@
       <c r="CY77" s="4"/>
       <c r="CZ77" s="4"/>
       <c r="DA77" s="4"/>
+      <c r="DB77" s="4"/>
     </row>
     <row r="78" spans="1:175" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A78" s="3" t="s">
@@ -10967,12 +11035,14 @@
       <c r="CY78" s="4"/>
       <c r="CZ78" s="4"/>
       <c r="DA78" s="4"/>
+      <c r="DB78" s="4"/>
     </row>
     <row r="79" spans="1:175" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="CX79" s="4"/>
       <c r="CY79" s="4"/>
       <c r="CZ79" s="4"/>
       <c r="DA79" s="4"/>
+      <c r="DB79" s="4"/>
     </row>
     <row r="80" spans="1:175" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A80" s="3" t="s">
@@ -11148,6 +11218,9 @@
       <c r="CY84" s="28"/>
       <c r="CZ84" s="28"/>
       <c r="DA84" s="28"/>
+      <c r="DB84" s="28">
+        <v>2026</v>
+      </c>
     </row>
     <row r="85" spans="1:179" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A85" s="5" t="s">
@@ -11464,6 +11537,9 @@
       </c>
       <c r="DA85" s="12" t="s">
         <v>5</v>
+      </c>
+      <c r="DB85" s="12" t="s">
+        <v>2</v>
       </c>
     </row>
     <row r="86" spans="1:179" s="3" customFormat="1" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
@@ -11785,7 +11861,9 @@
       <c r="DA87" s="13">
         <v>118.69705000291918</v>
       </c>
-      <c r="DB87" s="16"/>
+      <c r="DB87" s="13">
+        <v>116.51453453761545</v>
+      </c>
       <c r="DC87" s="16"/>
       <c r="DD87" s="16"/>
       <c r="DE87" s="16"/>
@@ -12176,7 +12254,9 @@
       <c r="DA88" s="13">
         <v>102.35330203033834</v>
       </c>
-      <c r="DB88" s="16"/>
+      <c r="DB88" s="13">
+        <v>101.22223924550345</v>
+      </c>
       <c r="DC88" s="16"/>
       <c r="DD88" s="16"/>
       <c r="DE88" s="16"/>
@@ -12356,7 +12436,7 @@
       <c r="CY89" s="8"/>
       <c r="CZ89" s="8"/>
       <c r="DA89" s="8"/>
-      <c r="DB89" s="16"/>
+      <c r="DB89" s="8"/>
       <c r="DC89" s="16"/>
       <c r="DD89" s="16"/>
       <c r="DE89" s="16"/>
@@ -12747,7 +12827,9 @@
       <c r="DA90" s="13">
         <v>103.66202270189</v>
       </c>
-      <c r="DB90" s="16"/>
+      <c r="DB90" s="13">
+        <v>102.37198423116109</v>
+      </c>
       <c r="DC90" s="16"/>
       <c r="DD90" s="16"/>
       <c r="DE90" s="16"/>
@@ -12928,6 +13010,7 @@
       <c r="CY91" s="10"/>
       <c r="CZ91" s="10"/>
       <c r="DA91" s="10"/>
+      <c r="DB91" s="10"/>
     </row>
     <row r="92" spans="1:179" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A92" s="11" t="s">
@@ -13124,6 +13207,9 @@
       <c r="CY103" s="28"/>
       <c r="CZ103" s="28"/>
       <c r="DA103" s="28"/>
+      <c r="DB103" s="28">
+        <v>2026</v>
+      </c>
     </row>
     <row r="104" spans="1:179" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A104" s="5" t="s">
@@ -13440,6 +13526,9 @@
       </c>
       <c r="DA104" s="12" t="s">
         <v>5</v>
+      </c>
+      <c r="DB104" s="12" t="s">
+        <v>2</v>
       </c>
     </row>
     <row r="105" spans="1:179" s="3" customFormat="1" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
@@ -13761,7 +13850,9 @@
       <c r="DA106" s="13">
         <v>9.1688644509590738</v>
       </c>
-      <c r="DB106" s="16"/>
+      <c r="DB106" s="13">
+        <v>8.5571241319573339</v>
+      </c>
       <c r="DC106" s="16"/>
       <c r="DD106" s="16"/>
       <c r="DE106" s="16"/>
@@ -14152,7 +14243,9 @@
       <c r="DA107" s="13">
         <v>90.831135549040923</v>
       </c>
-      <c r="DB107" s="16"/>
+      <c r="DB107" s="13">
+        <v>91.442875868042663</v>
+      </c>
       <c r="DC107" s="16"/>
       <c r="DD107" s="16"/>
       <c r="DE107" s="16"/>
@@ -14332,7 +14425,7 @@
       <c r="CY108" s="8"/>
       <c r="CZ108" s="8"/>
       <c r="DA108" s="8"/>
-      <c r="DB108" s="16"/>
+      <c r="DB108" s="8"/>
       <c r="DC108" s="16"/>
       <c r="DD108" s="16"/>
       <c r="DE108" s="16"/>
@@ -14723,7 +14816,9 @@
       <c r="DA109" s="13">
         <v>100</v>
       </c>
-      <c r="DB109" s="16"/>
+      <c r="DB109" s="13">
+        <v>100</v>
+      </c>
       <c r="DC109" s="16"/>
       <c r="DD109" s="16"/>
       <c r="DE109" s="16"/>
@@ -14904,6 +14999,7 @@
       <c r="CY110" s="10"/>
       <c r="CZ110" s="10"/>
       <c r="DA110" s="10"/>
+      <c r="DB110" s="10"/>
     </row>
     <row r="111" spans="1:179" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A111" s="11" t="s">
@@ -15460,6 +15556,9 @@
       <c r="CY122" s="28"/>
       <c r="CZ122" s="28"/>
       <c r="DA122" s="28"/>
+      <c r="DB122" s="28">
+        <v>2026</v>
+      </c>
     </row>
     <row r="123" spans="1:179" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A123" s="5" t="s">
@@ -15776,6 +15875,9 @@
       </c>
       <c r="DA123" s="12" t="s">
         <v>5</v>
+      </c>
+      <c r="DB123" s="12" t="s">
+        <v>2</v>
       </c>
     </row>
     <row r="124" spans="1:179" s="3" customFormat="1" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
@@ -16097,7 +16199,9 @@
       <c r="DA125" s="13">
         <v>8.0074697293866723</v>
       </c>
-      <c r="DB125" s="16"/>
+      <c r="DB125" s="13">
+        <v>7.5184592220811215</v>
+      </c>
       <c r="DC125" s="16"/>
       <c r="DD125" s="16"/>
       <c r="DE125" s="16"/>
@@ -16488,7 +16592,9 @@
       <c r="DA126" s="13">
         <v>91.992530270613344</v>
       </c>
-      <c r="DB126" s="16"/>
+      <c r="DB126" s="13">
+        <v>92.481540777918866</v>
+      </c>
       <c r="DC126" s="16"/>
       <c r="DD126" s="16"/>
       <c r="DE126" s="16"/>
@@ -16668,7 +16774,7 @@
       <c r="CY127" s="8"/>
       <c r="CZ127" s="8"/>
       <c r="DA127" s="8"/>
-      <c r="DB127" s="16"/>
+      <c r="DB127" s="8"/>
       <c r="DC127" s="16"/>
       <c r="DD127" s="16"/>
       <c r="DE127" s="16"/>
@@ -17059,7 +17165,9 @@
       <c r="DA128" s="13">
         <v>100</v>
       </c>
-      <c r="DB128" s="16"/>
+      <c r="DB128" s="13">
+        <v>100</v>
+      </c>
       <c r="DC128" s="16"/>
       <c r="DD128" s="16"/>
       <c r="DE128" s="16"/>
@@ -17240,6 +17348,7 @@
       <c r="CY129" s="10"/>
       <c r="CZ129" s="10"/>
       <c r="DA129" s="10"/>
+      <c r="DB129" s="10"/>
     </row>
     <row r="130" spans="1:179" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A130" s="11" t="s">
@@ -17352,7 +17461,7 @@
       <c r="CY131" s="26"/>
       <c r="CZ131" s="26"/>
       <c r="DA131" s="26"/>
-      <c r="DB131" s="25"/>
+      <c r="DB131" s="26"/>
       <c r="DC131" s="25"/>
       <c r="DD131" s="25"/>
       <c r="DE131" s="25"/>
@@ -17433,6 +17542,7 @@
       <c r="CX132" s="18"/>
       <c r="CZ132" s="18"/>
       <c r="DA132" s="18"/>
+      <c r="DB132" s="18"/>
     </row>
     <row r="133" spans="1:179" x14ac:dyDescent="0.2">
       <c r="CT133" s="18"/>
@@ -17442,6 +17552,7 @@
       <c r="CY133" s="18"/>
       <c r="CZ133" s="18"/>
       <c r="DA133" s="18"/>
+      <c r="DB133" s="18"/>
     </row>
     <row r="134" spans="1:179" x14ac:dyDescent="0.2">
       <c r="CT134" s="18"/>
@@ -17451,6 +17562,7 @@
       <c r="CY134" s="18"/>
       <c r="CZ134" s="18"/>
       <c r="DA134" s="18"/>
+      <c r="DB134" s="18"/>
     </row>
     <row r="135" spans="1:179" x14ac:dyDescent="0.2">
       <c r="CT135" s="18"/>
@@ -17460,6 +17572,7 @@
       <c r="CY135" s="18"/>
       <c r="CZ135" s="18"/>
       <c r="DA135" s="18"/>
+      <c r="DB135" s="18"/>
     </row>
     <row r="136" spans="1:179" x14ac:dyDescent="0.2">
       <c r="CT136" s="18"/>
@@ -17469,6 +17582,7 @@
       <c r="CY136" s="18"/>
       <c r="CZ136" s="18"/>
       <c r="DA136" s="18"/>
+      <c r="DB136" s="18"/>
     </row>
     <row r="137" spans="1:179" x14ac:dyDescent="0.2">
       <c r="CT137" s="18"/>
@@ -17478,6 +17592,7 @@
       <c r="CY137" s="18"/>
       <c r="CZ137" s="18"/>
       <c r="DA137" s="18"/>
+      <c r="DB137" s="18"/>
     </row>
     <row r="138" spans="1:179" x14ac:dyDescent="0.2">
       <c r="CT138" s="18"/>
@@ -17487,6 +17602,7 @@
       <c r="CY138" s="18"/>
       <c r="CZ138" s="18"/>
       <c r="DA138" s="18"/>
+      <c r="DB138" s="18"/>
     </row>
     <row r="139" spans="1:179" x14ac:dyDescent="0.2">
       <c r="CT139" s="18"/>
@@ -17512,9 +17628,9 @@
   <pageSetup paperSize="9" scale="39" orientation="landscape" r:id="rId1"/>
   <headerFooter alignWithMargins="0"/>
   <rowBreaks count="3" manualBreakCount="3">
-    <brk id="38" max="81" man="1"/>
-    <brk id="76" max="81" man="1"/>
-    <brk id="94" max="81" man="1"/>
+    <brk id="38" max="105" man="1"/>
+    <brk id="76" max="105" man="1"/>
+    <brk id="94" max="105" man="1"/>
   </rowBreaks>
 </worksheet>
 </file>
--- a/Data/National Accounts/PSA-16IAC_2018PSNA_Qrt.xlsx
+++ b/Data/National Accounts/PSA-16IAC_2018PSNA_Qrt.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\Shared drives\QNAP\NAP Dissemination\As of May 2026\Tables\NAP Q1 2000 to Q1 2026\Qtr\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\Shared drives\QNAP\NAP Dissemination\As of August 2026\Tables\NAP Q1 2000 to Q2 2026\Qtr\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F207A125-3B0C-41FB-9777-0CC002C2BCB4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2FC580AD-F9F8-487D-A502-AE4A831C686E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="794" xr2:uid="{736930C2-BFBB-46C3-AE9E-AECFC8C3145D}"/>
   </bookViews>
@@ -353,7 +353,7 @@
     <definedName name="pet">#REF!</definedName>
     <definedName name="plastic">#REF!</definedName>
     <definedName name="ply">#REF!</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">IAC!$A$1:$DB$131</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">IAC!$A$1:$DC$131</definedName>
     <definedName name="_xlnm.Print_Area">#REF!</definedName>
     <definedName name="PRINT_AREA_MI">#REF!</definedName>
     <definedName name="Print_Titles_MI">#REF!,#REF!</definedName>
@@ -527,7 +527,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="855" uniqueCount="54">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="862" uniqueCount="54">
   <si>
     <t>National Accounts of the Philippines</t>
   </si>
@@ -683,13 +683,13 @@
     <t>Table 17.7 Gross Value Added in Information and Communication, by Industry</t>
   </si>
   <si>
-    <t>Q1 2000 to Q1 2026</t>
+    <t>2025 - 2026</t>
   </si>
   <si>
-    <t>As of May 2026</t>
+    <t>Q1 2000 to Q2 2026</t>
   </si>
   <si>
-    <t>2025 - 2026</t>
+    <t>As of August 2026</t>
   </si>
 </sst>
 </file>
@@ -1218,8 +1218,8 @@
   <sheetFormatPr defaultColWidth="10" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="61.28515625" style="3" customWidth="1"/>
-    <col min="2" max="106" width="13" style="17" customWidth="1"/>
-    <col min="107" max="16384" width="10" style="17"/>
+    <col min="2" max="107" width="13" style="17" customWidth="1"/>
+    <col min="108" max="16384" width="10" style="17"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:179" s="3" customFormat="1" x14ac:dyDescent="0.2">
@@ -1234,7 +1234,7 @@
     </row>
     <row r="3" spans="1:179" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A3" s="2" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="4" spans="1:179" s="3" customFormat="1" x14ac:dyDescent="0.2"/>
@@ -1245,7 +1245,7 @@
     </row>
     <row r="6" spans="1:179" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A6" s="1" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="7" spans="1:179" s="3" customFormat="1" x14ac:dyDescent="0.2">
@@ -1357,6 +1357,7 @@
       <c r="CZ7" s="21"/>
       <c r="DA7" s="21"/>
       <c r="DB7" s="21"/>
+      <c r="DC7" s="21"/>
     </row>
     <row r="8" spans="1:179" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B8" s="21"/>
@@ -1464,6 +1465,7 @@
       <c r="CZ8" s="21"/>
       <c r="DA8" s="21"/>
       <c r="DB8" s="21"/>
+      <c r="DC8" s="21"/>
     </row>
     <row r="9" spans="1:179" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A9" s="14"/>
@@ -1626,6 +1628,7 @@
       <c r="DB9" s="28">
         <v>2026</v>
       </c>
+      <c r="DC9" s="28"/>
     </row>
     <row r="10" spans="1:179" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A10" s="5" t="s">
@@ -1945,6 +1948,9 @@
       </c>
       <c r="DB10" s="12" t="s">
         <v>2</v>
+      </c>
+      <c r="DC10" s="12" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="11" spans="1:179" s="3" customFormat="1" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
@@ -2267,9 +2273,11 @@
         <v>20564.848885990174</v>
       </c>
       <c r="DB12" s="20">
-        <v>16493.870679350446</v>
-      </c>
-      <c r="DC12" s="16"/>
+        <v>15778.035118349198</v>
+      </c>
+      <c r="DC12" s="20">
+        <v>22640.749558971016</v>
+      </c>
       <c r="DD12" s="16"/>
       <c r="DE12" s="16"/>
       <c r="DF12" s="16"/>
@@ -2660,9 +2668,11 @@
         <v>203725.1817495818</v>
       </c>
       <c r="DB13" s="22">
-        <v>176256.2919337246</v>
-      </c>
-      <c r="DC13" s="16"/>
+        <v>176437.83943468527</v>
+      </c>
+      <c r="DC13" s="22">
+        <v>211068.87894115879</v>
+      </c>
       <c r="DD13" s="16"/>
       <c r="DE13" s="16"/>
       <c r="DF13" s="16"/>
@@ -2842,7 +2852,7 @@
       <c r="CZ14" s="23"/>
       <c r="DA14" s="23"/>
       <c r="DB14" s="23"/>
-      <c r="DC14" s="16"/>
+      <c r="DC14" s="23"/>
       <c r="DD14" s="16"/>
       <c r="DE14" s="16"/>
       <c r="DF14" s="16"/>
@@ -3233,9 +3243,11 @@
         <v>224290.03063557198</v>
       </c>
       <c r="DB15" s="24">
-        <v>192750.16261307505</v>
-      </c>
-      <c r="DC15" s="16"/>
+        <v>192215.87455303446</v>
+      </c>
+      <c r="DC15" s="24">
+        <v>233709.62850012979</v>
+      </c>
       <c r="DD15" s="16"/>
       <c r="DE15" s="16"/>
       <c r="DF15" s="16"/>
@@ -3416,6 +3428,7 @@
       <c r="CZ16" s="10"/>
       <c r="DA16" s="10"/>
       <c r="DB16" s="10"/>
+      <c r="DC16" s="10"/>
     </row>
     <row r="17" spans="1:179" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A17" s="11" t="s">
@@ -3794,7 +3807,7 @@
     </row>
     <row r="22" spans="1:179" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A22" s="3" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="23" spans="1:179" s="3" customFormat="1" x14ac:dyDescent="0.2"/>
@@ -3805,7 +3818,7 @@
     </row>
     <row r="25" spans="1:179" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A25" s="3" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="26" spans="1:179" s="3" customFormat="1" x14ac:dyDescent="0.2">
@@ -3917,6 +3930,7 @@
       <c r="CZ26" s="21"/>
       <c r="DA26" s="21"/>
       <c r="DB26" s="21"/>
+      <c r="DC26" s="21"/>
     </row>
     <row r="27" spans="1:179" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B27" s="21"/>
@@ -4024,6 +4038,7 @@
       <c r="CZ27" s="21"/>
       <c r="DA27" s="21"/>
       <c r="DB27" s="21"/>
+      <c r="DC27" s="21"/>
     </row>
     <row r="28" spans="1:179" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A28" s="14"/>
@@ -4186,6 +4201,7 @@
       <c r="DB28" s="28">
         <v>2026</v>
       </c>
+      <c r="DC28" s="28"/>
     </row>
     <row r="29" spans="1:179" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A29" s="5" t="s">
@@ -4505,6 +4521,9 @@
       </c>
       <c r="DB29" s="12" t="s">
         <v>2</v>
+      </c>
+      <c r="DC29" s="12" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="30" spans="1:179" s="3" customFormat="1" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
@@ -4827,9 +4846,11 @@
         <v>17325.492828578645</v>
       </c>
       <c r="DB31" s="20">
-        <v>14156.062799208608</v>
-      </c>
-      <c r="DC31" s="16"/>
+        <v>13594.25048088975</v>
+      </c>
+      <c r="DC31" s="20">
+        <v>21234.408092236332</v>
+      </c>
       <c r="DD31" s="16"/>
       <c r="DE31" s="16"/>
       <c r="DF31" s="16"/>
@@ -5220,9 +5241,11 @@
         <v>199041.14250187651</v>
       </c>
       <c r="DB32" s="22">
-        <v>174128.03080381802</v>
-      </c>
-      <c r="DC32" s="16"/>
+        <v>174307.38615330833</v>
+      </c>
+      <c r="DC32" s="22">
+        <v>209159.73055864507</v>
+      </c>
       <c r="DD32" s="16"/>
       <c r="DE32" s="16"/>
       <c r="DF32" s="16"/>
@@ -5793,9 +5816,11 @@
         <v>216366.63533045514</v>
       </c>
       <c r="DB34" s="24">
-        <v>188284.09360302665</v>
-      </c>
-      <c r="DC34" s="16"/>
+        <v>187901.63663419808</v>
+      </c>
+      <c r="DC34" s="24">
+        <v>230394.13865088139</v>
+      </c>
       <c r="DD34" s="16"/>
       <c r="DE34" s="16"/>
       <c r="DF34" s="16"/>
@@ -5976,6 +6001,7 @@
       <c r="CZ35" s="10"/>
       <c r="DA35" s="10"/>
       <c r="DB35" s="10"/>
+      <c r="DC35" s="10"/>
     </row>
     <row r="36" spans="1:179" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A36" s="11" t="s">
@@ -6268,7 +6294,7 @@
       <c r="CZ38" s="15"/>
       <c r="DA38" s="15"/>
       <c r="DB38" s="15"/>
-      <c r="DC38" s="16"/>
+      <c r="DC38" s="15"/>
       <c r="DD38" s="16"/>
       <c r="DE38" s="16"/>
       <c r="DF38" s="16"/>
@@ -6351,6 +6377,7 @@
       <c r="CZ39" s="4"/>
       <c r="DA39" s="4"/>
       <c r="DB39" s="4"/>
+      <c r="DC39" s="4"/>
     </row>
     <row r="40" spans="1:179" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A40" s="3" t="s">
@@ -6361,16 +6388,18 @@
       <c r="CZ40" s="4"/>
       <c r="DA40" s="4"/>
       <c r="DB40" s="4"/>
+      <c r="DC40" s="4"/>
     </row>
     <row r="41" spans="1:179" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A41" s="3" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="CX41" s="4"/>
       <c r="CY41" s="4"/>
       <c r="CZ41" s="4"/>
       <c r="DA41" s="4"/>
       <c r="DB41" s="4"/>
+      <c r="DC41" s="4"/>
     </row>
     <row r="42" spans="1:179" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="CX42" s="4"/>
@@ -6378,6 +6407,7 @@
       <c r="CZ42" s="4"/>
       <c r="DA42" s="4"/>
       <c r="DB42" s="4"/>
+      <c r="DC42" s="4"/>
     </row>
     <row r="43" spans="1:179" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A43" s="3" t="s">
@@ -6388,16 +6418,18 @@
       <c r="CZ43" s="4"/>
       <c r="DA43" s="4"/>
       <c r="DB43" s="4"/>
+      <c r="DC43" s="4"/>
     </row>
     <row r="44" spans="1:179" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A44" s="1" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="CX44" s="4"/>
       <c r="CY44" s="4"/>
       <c r="CZ44" s="4"/>
       <c r="DA44" s="4"/>
       <c r="DB44" s="4"/>
+      <c r="DC44" s="4"/>
     </row>
     <row r="45" spans="1:179" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A45" s="3" t="s">
@@ -6408,13 +6440,14 @@
       <c r="CZ45" s="4"/>
       <c r="DA45" s="4"/>
       <c r="DB45" s="4"/>
+      <c r="DC45" s="4"/>
     </row>
     <row r="46" spans="1:179" s="3" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="CX46" s="4"/>
       <c r="CY46" s="4"/>
       <c r="CZ46" s="4"/>
       <c r="DA46" s="4"/>
       <c r="DB46" s="4"/>
+      <c r="DC46" s="4"/>
     </row>
     <row r="47" spans="1:179" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A47" s="14"/>
@@ -6569,12 +6602,13 @@
       <c r="CV47" s="28"/>
       <c r="CW47" s="28"/>
       <c r="CX47" s="28" t="s">
-        <v>53</v>
-      </c>
-      <c r="CY47" s="29"/>
+        <v>51</v>
+      </c>
+      <c r="CY47" s="28"/>
       <c r="CZ47" s="29"/>
       <c r="DA47" s="29"/>
       <c r="DB47" s="29"/>
+      <c r="DC47" s="29"/>
     </row>
     <row r="48" spans="1:179" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A48" s="5" t="s">
@@ -6883,17 +6917,20 @@
       <c r="CX48" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="CY48" s="30"/>
+      <c r="CY48" s="5" t="s">
+        <v>3</v>
+      </c>
       <c r="CZ48" s="30"/>
       <c r="DA48" s="30"/>
       <c r="DB48" s="30"/>
+      <c r="DC48" s="30"/>
     </row>
     <row r="49" spans="1:175" s="3" customFormat="1" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A49" s="6"/>
-      <c r="CY49" s="4"/>
       <c r="CZ49" s="4"/>
       <c r="DA49" s="4"/>
       <c r="DB49" s="4"/>
+      <c r="DC49" s="4"/>
     </row>
     <row r="50" spans="1:175" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A50" s="3" t="s">
@@ -7200,13 +7237,15 @@
         <v>9.2850502381802045</v>
       </c>
       <c r="CX50" s="13">
-        <v>10.885116529562296</v>
-      </c>
-      <c r="CY50" s="19"/>
+        <v>6.0726918937245671</v>
+      </c>
+      <c r="CY50" s="13">
+        <v>6.4333418447226904</v>
+      </c>
       <c r="CZ50" s="19"/>
       <c r="DA50" s="19"/>
       <c r="DB50" s="19"/>
-      <c r="DC50" s="16"/>
+      <c r="DC50" s="19"/>
       <c r="DD50" s="16"/>
       <c r="DE50" s="16"/>
       <c r="DF50" s="16"/>
@@ -7581,13 +7620,15 @@
         <v>3.9910660612451352</v>
       </c>
       <c r="CX51" s="13">
-        <v>4.9693013716344723</v>
-      </c>
-      <c r="CY51" s="19"/>
+        <v>5.0774218485407658</v>
+      </c>
+      <c r="CY51" s="13">
+        <v>4.1788197094933253</v>
+      </c>
       <c r="CZ51" s="19"/>
       <c r="DA51" s="19"/>
       <c r="DB51" s="19"/>
-      <c r="DC51" s="16"/>
+      <c r="DC51" s="19"/>
       <c r="DD51" s="16"/>
       <c r="DE51" s="16"/>
       <c r="DF51" s="16"/>
@@ -7760,11 +7801,11 @@
       <c r="CV52" s="8"/>
       <c r="CW52" s="8"/>
       <c r="CX52" s="8"/>
-      <c r="CY52" s="7"/>
+      <c r="CY52" s="8"/>
       <c r="CZ52" s="7"/>
       <c r="DA52" s="7"/>
       <c r="DB52" s="7"/>
-      <c r="DC52" s="16"/>
+      <c r="DC52" s="7"/>
       <c r="DD52" s="16"/>
       <c r="DE52" s="16"/>
       <c r="DF52" s="16"/>
@@ -8139,13 +8180,15 @@
         <v>4.4550112927649508</v>
       </c>
       <c r="CX53" s="13">
-        <v>5.4507153550597423</v>
-      </c>
-      <c r="CY53" s="19"/>
+        <v>5.1584143921285346</v>
+      </c>
+      <c r="CY53" s="13">
+        <v>4.3930409596875393</v>
+      </c>
       <c r="CZ53" s="19"/>
       <c r="DA53" s="19"/>
       <c r="DB53" s="19"/>
-      <c r="DC53" s="16"/>
+      <c r="DC53" s="19"/>
       <c r="DD53" s="16"/>
       <c r="DE53" s="16"/>
       <c r="DF53" s="16"/>
@@ -8318,19 +8361,20 @@
       <c r="CV54" s="10"/>
       <c r="CW54" s="10"/>
       <c r="CX54" s="10"/>
-      <c r="CY54" s="31"/>
+      <c r="CY54" s="10"/>
       <c r="CZ54" s="31"/>
       <c r="DA54" s="31"/>
       <c r="DB54" s="31"/>
+      <c r="DC54" s="31"/>
     </row>
     <row r="55" spans="1:175" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A55" s="11" t="s">
         <v>6</v>
       </c>
-      <c r="CY55" s="4"/>
       <c r="CZ55" s="4"/>
       <c r="DA55" s="4"/>
       <c r="DB55" s="4"/>
+      <c r="DC55" s="4"/>
     </row>
     <row r="56" spans="1:175" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B56" s="16"/>
@@ -8434,11 +8478,11 @@
       <c r="CV56" s="16"/>
       <c r="CW56" s="16"/>
       <c r="CX56" s="16"/>
-      <c r="CY56" s="15"/>
+      <c r="CY56" s="16"/>
       <c r="CZ56" s="15"/>
       <c r="DA56" s="15"/>
       <c r="DB56" s="15"/>
-      <c r="DC56" s="16"/>
+      <c r="DC56" s="15"/>
       <c r="DD56" s="16"/>
       <c r="DE56" s="16"/>
       <c r="DF56" s="16"/>
@@ -8610,11 +8654,11 @@
       <c r="CV57" s="16"/>
       <c r="CW57" s="16"/>
       <c r="CX57" s="16"/>
-      <c r="CY57" s="15"/>
+      <c r="CY57" s="16"/>
       <c r="CZ57" s="15"/>
       <c r="DA57" s="15"/>
       <c r="DB57" s="15"/>
-      <c r="DC57" s="16"/>
+      <c r="DC57" s="15"/>
       <c r="DD57" s="16"/>
       <c r="DE57" s="16"/>
       <c r="DF57" s="16"/>
@@ -8688,67 +8732,67 @@
       <c r="A58" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="CY58" s="4"/>
       <c r="CZ58" s="4"/>
       <c r="DA58" s="4"/>
       <c r="DB58" s="4"/>
+      <c r="DC58" s="4"/>
     </row>
     <row r="59" spans="1:175" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A59" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="CY59" s="4"/>
       <c r="CZ59" s="4"/>
       <c r="DA59" s="4"/>
       <c r="DB59" s="4"/>
+      <c r="DC59" s="4"/>
     </row>
     <row r="60" spans="1:175" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A60" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="CY60" s="4"/>
+        <v>53</v>
+      </c>
       <c r="CZ60" s="4"/>
       <c r="DA60" s="4"/>
       <c r="DB60" s="4"/>
+      <c r="DC60" s="4"/>
     </row>
     <row r="61" spans="1:175" s="3" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="CY61" s="4"/>
       <c r="CZ61" s="4"/>
       <c r="DA61" s="4"/>
       <c r="DB61" s="4"/>
+      <c r="DC61" s="4"/>
     </row>
     <row r="62" spans="1:175" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A62" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="CY62" s="4"/>
       <c r="CZ62" s="4"/>
       <c r="DA62" s="4"/>
       <c r="DB62" s="4"/>
+      <c r="DC62" s="4"/>
     </row>
     <row r="63" spans="1:175" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A63" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="CY63" s="4"/>
+        <v>52</v>
+      </c>
       <c r="CZ63" s="4"/>
       <c r="DA63" s="4"/>
       <c r="DB63" s="4"/>
+      <c r="DC63" s="4"/>
     </row>
     <row r="64" spans="1:175" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A64" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="CY64" s="4"/>
       <c r="CZ64" s="4"/>
       <c r="DA64" s="4"/>
       <c r="DB64" s="4"/>
+      <c r="DC64" s="4"/>
     </row>
     <row r="65" spans="1:175" s="3" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="CY65" s="4"/>
       <c r="CZ65" s="4"/>
       <c r="DA65" s="4"/>
       <c r="DB65" s="4"/>
+      <c r="DC65" s="4"/>
     </row>
     <row r="66" spans="1:175" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A66" s="14"/>
@@ -8903,12 +8947,13 @@
       <c r="CV66" s="28"/>
       <c r="CW66" s="28"/>
       <c r="CX66" s="28" t="s">
-        <v>53</v>
-      </c>
-      <c r="CY66" s="29"/>
+        <v>51</v>
+      </c>
+      <c r="CY66" s="28"/>
       <c r="CZ66" s="29"/>
       <c r="DA66" s="29"/>
       <c r="DB66" s="29"/>
+      <c r="DC66" s="29"/>
     </row>
     <row r="67" spans="1:175" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A67" s="5" t="s">
@@ -9217,17 +9262,20 @@
       <c r="CX67" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="CY67" s="30"/>
+      <c r="CY67" s="5" t="s">
+        <v>3</v>
+      </c>
       <c r="CZ67" s="30"/>
       <c r="DA67" s="30"/>
       <c r="DB67" s="30"/>
+      <c r="DC67" s="30"/>
     </row>
     <row r="68" spans="1:175" s="3" customFormat="1" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A68" s="6"/>
-      <c r="CY68" s="4"/>
       <c r="CZ68" s="4"/>
       <c r="DA68" s="4"/>
       <c r="DB68" s="4"/>
+      <c r="DC68" s="4"/>
     </row>
     <row r="69" spans="1:175" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A69" s="3" t="s">
@@ -9534,13 +9582,15 @@
         <v>8.1433725480735148</v>
       </c>
       <c r="CX69" s="13">
-        <v>8.1910099163317938</v>
-      </c>
-      <c r="CY69" s="19"/>
+        <v>3.8972283073839264</v>
+      </c>
+      <c r="CY69" s="13">
+        <v>4.3300331290597569</v>
+      </c>
       <c r="CZ69" s="19"/>
       <c r="DA69" s="19"/>
       <c r="DB69" s="19"/>
-      <c r="DC69" s="16"/>
+      <c r="DC69" s="19"/>
       <c r="DD69" s="16"/>
       <c r="DE69" s="16"/>
       <c r="DF69" s="16"/>
@@ -9915,13 +9965,15 @@
         <v>3.2884237229934996</v>
       </c>
       <c r="CX70" s="13">
-        <v>4.0939961004148984</v>
-      </c>
-      <c r="CY70" s="19"/>
+        <v>4.2012149954098561</v>
+      </c>
+      <c r="CY70" s="13">
+        <v>3.1463569821933675</v>
+      </c>
       <c r="CZ70" s="19"/>
       <c r="DA70" s="19"/>
       <c r="DB70" s="19"/>
-      <c r="DC70" s="16"/>
+      <c r="DC70" s="19"/>
       <c r="DD70" s="16"/>
       <c r="DE70" s="16"/>
       <c r="DF70" s="16"/>
@@ -10093,11 +10145,11 @@
       <c r="CV71" s="8"/>
       <c r="CW71" s="8"/>
       <c r="CX71" s="8"/>
-      <c r="CY71" s="7"/>
+      <c r="CY71" s="8"/>
       <c r="CZ71" s="7"/>
       <c r="DA71" s="7"/>
       <c r="DB71" s="7"/>
-      <c r="DC71" s="16"/>
+      <c r="DC71" s="7"/>
       <c r="DD71" s="16"/>
       <c r="DE71" s="16"/>
       <c r="DF71" s="16"/>
@@ -10472,13 +10524,15 @@
         <v>3.6610690987286745</v>
       </c>
       <c r="CX72" s="13">
-        <v>4.3912099436748946</v>
-      </c>
-      <c r="CY72" s="19"/>
+        <v>4.1791625796974614</v>
+      </c>
+      <c r="CY72" s="13">
+        <v>3.2543263458053815</v>
+      </c>
       <c r="CZ72" s="19"/>
       <c r="DA72" s="19"/>
       <c r="DB72" s="19"/>
-      <c r="DC72" s="16"/>
+      <c r="DC72" s="19"/>
       <c r="DD72" s="16"/>
       <c r="DE72" s="16"/>
       <c r="DF72" s="16"/>
@@ -10651,19 +10705,20 @@
       <c r="CV73" s="10"/>
       <c r="CW73" s="10"/>
       <c r="CX73" s="10"/>
-      <c r="CY73" s="31"/>
+      <c r="CY73" s="10"/>
       <c r="CZ73" s="31"/>
       <c r="DA73" s="31"/>
       <c r="DB73" s="31"/>
+      <c r="DC73" s="31"/>
     </row>
     <row r="74" spans="1:175" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A74" s="11" t="s">
         <v>6</v>
       </c>
-      <c r="CY74" s="4"/>
       <c r="CZ74" s="4"/>
       <c r="DA74" s="4"/>
       <c r="DB74" s="4"/>
+      <c r="DC74" s="4"/>
     </row>
     <row r="75" spans="1:175" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B75" s="16"/>
@@ -10767,11 +10822,11 @@
       <c r="CV75" s="16"/>
       <c r="CW75" s="16"/>
       <c r="CX75" s="15"/>
-      <c r="CY75" s="15"/>
+      <c r="CY75" s="16"/>
       <c r="CZ75" s="15"/>
       <c r="DA75" s="15"/>
       <c r="DB75" s="15"/>
-      <c r="DC75" s="16"/>
+      <c r="DC75" s="15"/>
       <c r="DD75" s="16"/>
       <c r="DE75" s="16"/>
       <c r="DF75" s="16"/>
@@ -10947,7 +11002,7 @@
       <c r="CZ76" s="15"/>
       <c r="DA76" s="15"/>
       <c r="DB76" s="15"/>
-      <c r="DC76" s="16"/>
+      <c r="DC76" s="15"/>
       <c r="DD76" s="16"/>
       <c r="DE76" s="16"/>
       <c r="DF76" s="16"/>
@@ -11026,16 +11081,18 @@
       <c r="CZ77" s="4"/>
       <c r="DA77" s="4"/>
       <c r="DB77" s="4"/>
+      <c r="DC77" s="4"/>
     </row>
     <row r="78" spans="1:175" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A78" s="3" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="CX78" s="4"/>
       <c r="CY78" s="4"/>
       <c r="CZ78" s="4"/>
       <c r="DA78" s="4"/>
       <c r="DB78" s="4"/>
+      <c r="DC78" s="4"/>
     </row>
     <row r="79" spans="1:175" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="CX79" s="4"/>
@@ -11043,6 +11100,7 @@
       <c r="CZ79" s="4"/>
       <c r="DA79" s="4"/>
       <c r="DB79" s="4"/>
+      <c r="DC79" s="4"/>
     </row>
     <row r="80" spans="1:175" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A80" s="3" t="s">
@@ -11051,7 +11109,7 @@
     </row>
     <row r="81" spans="1:179" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A81" s="3" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="82" spans="1:179" s="3" customFormat="1" x14ac:dyDescent="0.2">
@@ -11221,6 +11279,7 @@
       <c r="DB84" s="28">
         <v>2026</v>
       </c>
+      <c r="DC84" s="28"/>
     </row>
     <row r="85" spans="1:179" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A85" s="5" t="s">
@@ -11540,6 +11599,9 @@
       </c>
       <c r="DB85" s="12" t="s">
         <v>2</v>
+      </c>
+      <c r="DC85" s="12" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="86" spans="1:179" s="3" customFormat="1" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
@@ -11862,9 +11924,11 @@
         <v>118.69705000291918</v>
       </c>
       <c r="DB87" s="13">
-        <v>116.51453453761545</v>
-      </c>
-      <c r="DC87" s="16"/>
+        <v>116.06403119119604</v>
+      </c>
+      <c r="DC87" s="13">
+        <v>106.62293698334292</v>
+      </c>
       <c r="DD87" s="16"/>
       <c r="DE87" s="16"/>
       <c r="DF87" s="16"/>
@@ -12255,9 +12319,11 @@
         <v>102.35330203033834</v>
       </c>
       <c r="DB88" s="13">
-        <v>101.22223924550345</v>
-      </c>
-      <c r="DC88" s="16"/>
+        <v>101.22223924550342</v>
+      </c>
+      <c r="DC88" s="13">
+        <v>100.912770530644</v>
+      </c>
       <c r="DD88" s="16"/>
       <c r="DE88" s="16"/>
       <c r="DF88" s="16"/>
@@ -12437,7 +12503,7 @@
       <c r="CZ89" s="8"/>
       <c r="DA89" s="8"/>
       <c r="DB89" s="8"/>
-      <c r="DC89" s="16"/>
+      <c r="DC89" s="8"/>
       <c r="DD89" s="16"/>
       <c r="DE89" s="16"/>
       <c r="DF89" s="16"/>
@@ -12828,9 +12894,11 @@
         <v>103.66202270189</v>
       </c>
       <c r="DB90" s="13">
-        <v>102.37198423116109</v>
-      </c>
-      <c r="DC90" s="16"/>
+        <v>102.29600869695203</v>
+      </c>
+      <c r="DC90" s="13">
+        <v>101.43905130081126</v>
+      </c>
       <c r="DD90" s="16"/>
       <c r="DE90" s="16"/>
       <c r="DF90" s="16"/>
@@ -13011,6 +13079,7 @@
       <c r="CZ91" s="10"/>
       <c r="DA91" s="10"/>
       <c r="DB91" s="10"/>
+      <c r="DC91" s="10"/>
     </row>
     <row r="92" spans="1:179" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A92" s="11" t="s">
@@ -13029,7 +13098,7 @@
     </row>
     <row r="97" spans="1:179" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A97" s="3" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="98" spans="1:179" s="3" customFormat="1" x14ac:dyDescent="0.2"/>
@@ -13040,7 +13109,7 @@
     </row>
     <row r="100" spans="1:179" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A100" s="3" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="101" spans="1:179" s="3" customFormat="1" x14ac:dyDescent="0.2">
@@ -13210,6 +13279,7 @@
       <c r="DB103" s="28">
         <v>2026</v>
       </c>
+      <c r="DC103" s="28"/>
     </row>
     <row r="104" spans="1:179" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A104" s="5" t="s">
@@ -13529,6 +13599,9 @@
       </c>
       <c r="DB104" s="12" t="s">
         <v>2</v>
+      </c>
+      <c r="DC104" s="12" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="105" spans="1:179" s="3" customFormat="1" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
@@ -13851,9 +13924,11 @@
         <v>9.1688644509590738</v>
       </c>
       <c r="DB106" s="13">
-        <v>8.5571241319573339</v>
-      </c>
-      <c r="DC106" s="16"/>
+        <v>8.2084974277168072</v>
+      </c>
+      <c r="DC106" s="13">
+        <v>9.6875553242165395</v>
+      </c>
       <c r="DD106" s="16"/>
       <c r="DE106" s="16"/>
       <c r="DF106" s="16"/>
@@ -14244,9 +14319,11 @@
         <v>90.831135549040923</v>
       </c>
       <c r="DB107" s="13">
-        <v>91.442875868042663</v>
-      </c>
-      <c r="DC107" s="16"/>
+        <v>91.791502572283207</v>
+      </c>
+      <c r="DC107" s="13">
+        <v>90.312444675783468</v>
+      </c>
       <c r="DD107" s="16"/>
       <c r="DE107" s="16"/>
       <c r="DF107" s="16"/>
@@ -14426,7 +14503,7 @@
       <c r="CZ108" s="8"/>
       <c r="DA108" s="8"/>
       <c r="DB108" s="8"/>
-      <c r="DC108" s="16"/>
+      <c r="DC108" s="8"/>
       <c r="DD108" s="16"/>
       <c r="DE108" s="16"/>
       <c r="DF108" s="16"/>
@@ -14819,7 +14896,9 @@
       <c r="DB109" s="13">
         <v>100</v>
       </c>
-      <c r="DC109" s="16"/>
+      <c r="DC109" s="13">
+        <v>100</v>
+      </c>
       <c r="DD109" s="16"/>
       <c r="DE109" s="16"/>
       <c r="DF109" s="16"/>
@@ -15000,6 +15079,7 @@
       <c r="CZ110" s="10"/>
       <c r="DA110" s="10"/>
       <c r="DB110" s="10"/>
+      <c r="DC110" s="10"/>
     </row>
     <row r="111" spans="1:179" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A111" s="11" t="s">
@@ -15378,7 +15458,7 @@
     </row>
     <row r="116" spans="1:179" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A116" s="3" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="117" spans="1:179" s="3" customFormat="1" x14ac:dyDescent="0.2"/>
@@ -15389,7 +15469,7 @@
     </row>
     <row r="119" spans="1:179" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A119" s="3" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="120" spans="1:179" s="3" customFormat="1" x14ac:dyDescent="0.2">
@@ -15559,6 +15639,7 @@
       <c r="DB122" s="28">
         <v>2026</v>
       </c>
+      <c r="DC122" s="28"/>
     </row>
     <row r="123" spans="1:179" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A123" s="5" t="s">
@@ -15878,6 +15959,9 @@
       </c>
       <c r="DB123" s="12" t="s">
         <v>2</v>
+      </c>
+      <c r="DC123" s="12" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="124" spans="1:179" s="3" customFormat="1" ht="10.9" customHeight="1" x14ac:dyDescent="0.2">
@@ -16200,9 +16284,11 @@
         <v>8.0074697293866723</v>
       </c>
       <c r="DB125" s="13">
-        <v>7.5184592220811215</v>
-      </c>
-      <c r="DC125" s="16"/>
+        <v>7.2347695977521891</v>
+      </c>
+      <c r="DC125" s="13">
+        <v>9.2165574248453641</v>
+      </c>
       <c r="DD125" s="16"/>
       <c r="DE125" s="16"/>
       <c r="DF125" s="16"/>
@@ -16593,9 +16679,11 @@
         <v>91.992530270613344</v>
       </c>
       <c r="DB126" s="13">
-        <v>92.481540777918866</v>
-      </c>
-      <c r="DC126" s="16"/>
+        <v>92.765230402247809</v>
+      </c>
+      <c r="DC126" s="13">
+        <v>90.783442575154638</v>
+      </c>
       <c r="DD126" s="16"/>
       <c r="DE126" s="16"/>
       <c r="DF126" s="16"/>
@@ -16775,7 +16863,7 @@
       <c r="CZ127" s="8"/>
       <c r="DA127" s="8"/>
       <c r="DB127" s="8"/>
-      <c r="DC127" s="16"/>
+      <c r="DC127" s="8"/>
       <c r="DD127" s="16"/>
       <c r="DE127" s="16"/>
       <c r="DF127" s="16"/>
@@ -17168,7 +17256,9 @@
       <c r="DB128" s="13">
         <v>100</v>
       </c>
-      <c r="DC128" s="16"/>
+      <c r="DC128" s="13">
+        <v>100</v>
+      </c>
       <c r="DD128" s="16"/>
       <c r="DE128" s="16"/>
       <c r="DF128" s="16"/>
@@ -17349,6 +17439,7 @@
       <c r="CZ129" s="10"/>
       <c r="DA129" s="10"/>
       <c r="DB129" s="10"/>
+      <c r="DC129" s="10"/>
     </row>
     <row r="130" spans="1:179" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A130" s="11" t="s">
@@ -17462,7 +17553,7 @@
       <c r="CZ131" s="26"/>
       <c r="DA131" s="26"/>
       <c r="DB131" s="26"/>
-      <c r="DC131" s="25"/>
+      <c r="DC131" s="26"/>
       <c r="DD131" s="25"/>
       <c r="DE131" s="25"/>
       <c r="DF131" s="25"/>
@@ -17540,9 +17631,11 @@
       <c r="CT132" s="18"/>
       <c r="CV132" s="18"/>
       <c r="CX132" s="18"/>
+      <c r="CY132" s="18"/>
       <c r="CZ132" s="18"/>
       <c r="DA132" s="18"/>
       <c r="DB132" s="18"/>
+      <c r="DC132" s="18"/>
     </row>
     <row r="133" spans="1:179" x14ac:dyDescent="0.2">
       <c r="CT133" s="18"/>
@@ -17553,6 +17646,7 @@
       <c r="CZ133" s="18"/>
       <c r="DA133" s="18"/>
       <c r="DB133" s="18"/>
+      <c r="DC133" s="18"/>
     </row>
     <row r="134" spans="1:179" x14ac:dyDescent="0.2">
       <c r="CT134" s="18"/>
@@ -17563,6 +17657,7 @@
       <c r="CZ134" s="18"/>
       <c r="DA134" s="18"/>
       <c r="DB134" s="18"/>
+      <c r="DC134" s="18"/>
     </row>
     <row r="135" spans="1:179" x14ac:dyDescent="0.2">
       <c r="CT135" s="18"/>
@@ -17573,6 +17668,7 @@
       <c r="CZ135" s="18"/>
       <c r="DA135" s="18"/>
       <c r="DB135" s="18"/>
+      <c r="DC135" s="18"/>
     </row>
     <row r="136" spans="1:179" x14ac:dyDescent="0.2">
       <c r="CT136" s="18"/>
@@ -17583,6 +17679,7 @@
       <c r="CZ136" s="18"/>
       <c r="DA136" s="18"/>
       <c r="DB136" s="18"/>
+      <c r="DC136" s="18"/>
     </row>
     <row r="137" spans="1:179" x14ac:dyDescent="0.2">
       <c r="CT137" s="18"/>
@@ -17593,6 +17690,7 @@
       <c r="CZ137" s="18"/>
       <c r="DA137" s="18"/>
       <c r="DB137" s="18"/>
+      <c r="DC137" s="18"/>
     </row>
     <row r="138" spans="1:179" x14ac:dyDescent="0.2">
       <c r="CT138" s="18"/>
@@ -17603,6 +17701,7 @@
       <c r="CZ138" s="18"/>
       <c r="DA138" s="18"/>
       <c r="DB138" s="18"/>
+      <c r="DC138" s="18"/>
     </row>
     <row r="139" spans="1:179" x14ac:dyDescent="0.2">
       <c r="CT139" s="18"/>
@@ -17612,15 +17711,13 @@
       <c r="CY139" s="18"/>
       <c r="CZ139" s="18"/>
       <c r="DA139" s="18"/>
+      <c r="DB139" s="18"/>
+      <c r="DC139" s="18"/>
     </row>
     <row r="140" spans="1:179" x14ac:dyDescent="0.2">
       <c r="CT140" s="18"/>
       <c r="CU140" s="18"/>
       <c r="CV140" s="18"/>
-      <c r="CX140" s="18"/>
-      <c r="CY140" s="18"/>
-      <c r="CZ140" s="18"/>
-      <c r="DA140" s="18"/>
     </row>
   </sheetData>
   <printOptions horizontalCentered="1"/>
@@ -17628,9 +17725,9 @@
   <pageSetup paperSize="9" scale="39" orientation="landscape" r:id="rId1"/>
   <headerFooter alignWithMargins="0"/>
   <rowBreaks count="3" manualBreakCount="3">
-    <brk id="38" max="105" man="1"/>
-    <brk id="76" max="105" man="1"/>
-    <brk id="94" max="105" man="1"/>
+    <brk id="38" max="106" man="1"/>
+    <brk id="76" max="106" man="1"/>
+    <brk id="94" max="106" man="1"/>
   </rowBreaks>
 </worksheet>
 </file>